--- a/data/trending_integrated_20261007_12.xlsx
+++ b/data/trending_integrated_20261007_12.xlsx
@@ -578,10 +578,10 @@
         <v>-0.08</v>
       </c>
       <c r="E2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G2" t="n">
         <v>32</v>
@@ -610,7 +610,7 @@
         <v>3.35</v>
       </c>
       <c r="O2" t="n">
-        <v>26271723304</v>
+        <v>26301647954</v>
       </c>
       <c r="P2" t="n">
         <v>5470</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7740</v>
+        <v>8120</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+14.67%</t>
+          <t>'+20.30%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F3" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G3" t="n">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H3" t="n">
         <v>5.12</v>
@@ -702,7 +702,7 @@
         <v>5.14</v>
       </c>
       <c r="O3" t="n">
-        <v>63300726055</v>
+        <v>68937064430</v>
       </c>
       <c r="P3" t="n">
         <v>23500</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26150</v>
+        <v>26200</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+13.94%</t>
+          <t>'+14.16%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.4</v>
       </c>
       <c r="E4" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F4" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G4" t="n">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="H4" t="n">
         <v>2.82</v>
@@ -794,7 +794,7 @@
         <v>2.42</v>
       </c>
       <c r="O4" t="n">
-        <v>90841811975</v>
+        <v>91725587600</v>
       </c>
       <c r="P4" t="n">
         <v>30100</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16920</v>
+        <v>16900</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+13.79%</t>
+          <t>'+13.65%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.98</v>
       </c>
       <c r="E5" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F5" t="n">
         <v>82</v>
       </c>
       <c r="G5" t="n">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="H5" t="n">
         <v>2.37</v>
@@ -886,7 +886,7 @@
         <v>1.39</v>
       </c>
       <c r="O5" t="n">
-        <v>229745776055</v>
+        <v>234790001100</v>
       </c>
       <c r="P5" t="n">
         <v>17590</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>개인정보 유출 사고 증가 속 양자보안 기술 부각, 농협/KDB생명 공급 논의 등 긍정적 뉴스 다수 확인.</t>
+          <t>개인정보 유출 이슈에 따른 보안주 강세, 양자보안 기술 공급 논의 및 대장주 부각.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['양자보안', '개인정보 유출', '보안주']</t>
+          <t>['보안', '해킹', '양자보안']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,79 +931,79 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>신풍제약</t>
+          <t>셀리드</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10560</v>
+        <v>2640</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+9.20%</t>
+          <t>'+10.69%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.17</v>
+        <v>-0.29</v>
       </c>
       <c r="E6" t="n">
-        <v>103</v>
+        <v>39</v>
       </c>
       <c r="F6" t="n">
-        <v>66</v>
+        <v>20</v>
       </c>
       <c r="G6" t="n">
-        <v>315</v>
+        <v>60</v>
       </c>
       <c r="H6" t="n">
-        <v>5.01</v>
+        <v>0.82</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>9670</v>
+        <v>2385</v>
       </c>
       <c r="K6" t="n">
-        <v>11020</v>
+        <v>2510</v>
       </c>
       <c r="L6" t="n">
-        <v>11030</v>
+        <v>2900</v>
       </c>
       <c r="M6" t="n">
-        <v>10300</v>
+        <v>2505</v>
       </c>
       <c r="N6" t="n">
-        <v>4.84</v>
+        <v>1.11</v>
       </c>
       <c r="O6" t="n">
-        <v>16803191910</v>
+        <v>9047553326</v>
       </c>
       <c r="P6" t="n">
-        <v>15900</v>
+        <v>4760</v>
       </c>
       <c r="Q6" t="n">
-        <v>6310</v>
+        <v>973</v>
       </c>
       <c r="R6" t="n">
-        <v>-216000</v>
+        <v>-31000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>페스트, 에볼라 등 다양한 질병 테마주로 언급되며 상한가 기대감 형성. 모건의 매수세 확인.</t>
+          <t>바이오 섹터 전반의 부진 속에서의 기술적 반등 시도. 유상증자 관련 지분 매각 이슈.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['테마주', '페스트', '에볼라']</t>
+          <t>['바이오', '유상증자', '기술적 반등']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1011,91 +1011,91 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>019170</t>
+          <t>299660</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>신풍제약</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13430</v>
+        <v>10530</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+8.92%</t>
+          <t>'+8.89%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.31</v>
+        <v>0.17</v>
       </c>
       <c r="E7" t="n">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="F7" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="G7" t="n">
-        <v>127</v>
+        <v>317</v>
       </c>
       <c r="H7" t="n">
-        <v>0.79</v>
+        <v>5.01</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>12330</v>
+        <v>9670</v>
       </c>
       <c r="K7" t="n">
-        <v>12580</v>
+        <v>11020</v>
       </c>
       <c r="L7" t="n">
-        <v>14260</v>
+        <v>11030</v>
       </c>
       <c r="M7" t="n">
-        <v>12300</v>
+        <v>10300</v>
       </c>
       <c r="N7" t="n">
-        <v>0.48</v>
+        <v>4.84</v>
       </c>
       <c r="O7" t="n">
-        <v>166802780580</v>
+        <v>16900250260</v>
       </c>
       <c r="P7" t="n">
-        <v>20850</v>
+        <v>15900</v>
       </c>
       <c r="Q7" t="n">
-        <v>4020</v>
+        <v>6310</v>
       </c>
       <c r="R7" t="n">
-        <v>-65000</v>
+        <v>-216000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>한화파워 가스터빈 블레이드 납품 개시 및 원전, 데이터센터 관련 사업 언급. 14,200원 돌파 시 급등 예상 및 텐버거 기대감 표시. 거래량 증가 및 손바뀜 확인.</t>
+          <t>다양한 질병 테마 언급, 페스트/에볼라 확산 관련 기대와 우려 공존.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['가스터빈', '원전', '납품']</t>
+          <t>['테마', '확산', '기대']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1103,43 +1103,43 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>019170</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>셀리드</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2595</v>
+        <v>13220</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+8.81%</t>
+          <t>'+7.22%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.29</v>
+        <v>0.31</v>
       </c>
       <c r="E8" t="n">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="F8" t="n">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="G8" t="n">
-        <v>59</v>
+        <v>133</v>
       </c>
       <c r="H8" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,47 +1147,47 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>2385</v>
+        <v>12330</v>
       </c>
       <c r="K8" t="n">
-        <v>2510</v>
+        <v>12580</v>
       </c>
       <c r="L8" t="n">
-        <v>2900</v>
+        <v>14260</v>
       </c>
       <c r="M8" t="n">
-        <v>2505</v>
+        <v>12300</v>
       </c>
       <c r="N8" t="n">
-        <v>1.11</v>
+        <v>0.48</v>
       </c>
       <c r="O8" t="n">
-        <v>9004949451</v>
+        <v>170075291320</v>
       </c>
       <c r="P8" t="n">
-        <v>4760</v>
+        <v>20850</v>
       </c>
       <c r="Q8" t="n">
-        <v>973</v>
+        <v>4020</v>
       </c>
       <c r="R8" t="n">
-        <v>-31000</v>
+        <v>-65000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>바이오 섹터 전반의 부진 속에서의 기술적 반등 시도. 유상증자 관련 지분 매각 이슈.</t>
+          <t>가스터빈 블레이드 납품 개시 및 원전 관련 기대감, 단기 급등 가능성 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['바이오', '유상증자', '기술적 반등']</t>
+          <t>['납품', '원전', '기대']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>299660</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5070</v>
+        <v>5080</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+1.20%</t>
+          <t>'+1.40%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>3.32</v>
       </c>
       <c r="E9" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="F9" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G9" t="n">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="H9" t="n">
         <v>4.72</v>
@@ -1254,7 +1254,7 @@
         <v>1.4</v>
       </c>
       <c r="O9" t="n">
-        <v>198147080555</v>
+        <v>200309958730</v>
       </c>
       <c r="P9" t="n">
         <v>8100</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2200억 규모 수주 계약 선주문 가능성 언급, 미 증시 호조 및 개인 물량 매도세 관찰.</t>
+          <t>미국 시장 호조 및 2200억 규모 수주 계약 기대감, 주가 상승 전망.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['수주 계약', '선주문', '주가 전망']</t>
+          <t>['수주', '상승', '기대']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>272500</v>
+        <v>272000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.18%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="G10" t="n">
-        <v>1476</v>
+        <v>1432</v>
       </c>
       <c r="H10" t="n">
         <v>46.37</v>
@@ -1346,7 +1346,7 @@
         <v>46.41</v>
       </c>
       <c r="O10" t="n">
-        <v>2425812421250</v>
+        <v>2445050826250</v>
       </c>
       <c r="P10" t="n">
         <v>374500</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>정치적 이슈와 연관된 부정적 여론 속에서 소폭 상승했으나, 4개월간 30만원 돌파 실패. 매수 주체에 대한 의문 제기.</t>
+          <t>정치적 이슈와 연계된 부정적 전망, 일부 매수세 유입 기대.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['증시', '외인', '기관']</t>
+          <t>['매도', '매수', '정치']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>80900</v>
+        <v>81000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-0.74%</t>
+          <t>'-0.61%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.03</v>
       </c>
       <c r="E11" t="n">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="F11" t="n">
         <v>153</v>
       </c>
       <c r="G11" t="n">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="H11" t="n">
         <v>22.59</v>
@@ -1438,7 +1438,7 @@
         <v>22.56</v>
       </c>
       <c r="O11" t="n">
-        <v>124422884200</v>
+        <v>125225851150</v>
       </c>
       <c r="P11" t="n">
         <v>139200</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17490</v>
+        <v>17540</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.46%</t>
+          <t>'-1.18%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.11</v>
       </c>
       <c r="E12" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G12" t="n">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="H12" t="n">
         <v>9.5</v>
@@ -1530,7 +1530,7 @@
         <v>9.390000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>41771350120</v>
+        <v>42521687825</v>
       </c>
       <c r="P12" t="n">
         <v>40350</v>
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>237000</v>
+        <v>236500</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.66%</t>
+          <t>'-1.87%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1596,7 +1596,7 @@
         <v>108</v>
       </c>
       <c r="G13" t="n">
-        <v>827</v>
+        <v>856</v>
       </c>
       <c r="H13" t="n">
         <v>4.12</v>
@@ -1622,7 +1622,7 @@
         <v>4.08</v>
       </c>
       <c r="O13" t="n">
-        <v>79595582500</v>
+        <v>79973223500</v>
       </c>
       <c r="P13" t="n">
         <v>1233000</v>
@@ -1667,123 +1667,123 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6860</v>
+        <v>1739000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-1.72%</t>
+          <t>'-1.92%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.77</v>
+        <v>-0.05</v>
       </c>
       <c r="E14" t="n">
-        <v>68</v>
+        <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>46</v>
+        <v>436</v>
       </c>
       <c r="G14" t="n">
-        <v>187</v>
+        <v>1639</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1</v>
+        <v>49.71</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>6980</v>
+        <v>1773000</v>
       </c>
       <c r="K14" t="n">
-        <v>7000</v>
+        <v>1728000</v>
       </c>
       <c r="L14" t="n">
-        <v>7240</v>
+        <v>1779000</v>
       </c>
       <c r="M14" t="n">
-        <v>6580</v>
+        <v>1725000</v>
       </c>
       <c r="N14" t="n">
-        <v>1.87</v>
+        <v>49.76</v>
       </c>
       <c r="O14" t="n">
-        <v>46103756145</v>
+        <v>2444478998500</v>
       </c>
       <c r="P14" t="n">
-        <v>11370</v>
+        <v>2987000</v>
       </c>
       <c r="Q14" t="n">
-        <v>3300</v>
+        <v>403000</v>
       </c>
       <c r="R14" t="n">
-        <v>180000</v>
+        <v>-199000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-57000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>망분리 완화 관련 금융권 공략 소식 및 3분기 역대급 실적 기대감 언급. 라온시큐어와의 비교 및 보안주로서의 성장 가능성 제시. 시가총액 1조 달성.</t>
+          <t>외인 매도세 지속 및 추세선 하향 돌파, 정치적 이슈와 함께 부정적 전망.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['망분리', '보안주', '실적']</t>
+          <t>['매도', '추세', '하락']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>158430</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1742000</v>
+        <v>13120</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-1.75%</t>
+          <t>'-2.02%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.05</v>
+        <v>0.06</v>
       </c>
       <c r="E15" t="n">
-        <v>800</v>
+        <v>49</v>
       </c>
       <c r="F15" t="n">
-        <v>441</v>
+        <v>24</v>
       </c>
       <c r="G15" t="n">
-        <v>1589</v>
+        <v>82</v>
       </c>
       <c r="H15" t="n">
-        <v>49.71</v>
+        <v>3.18</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,130 +1791,130 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>1773000</v>
+        <v>13390</v>
       </c>
       <c r="K15" t="n">
-        <v>1728000</v>
+        <v>13770</v>
       </c>
       <c r="L15" t="n">
-        <v>1779000</v>
+        <v>13830</v>
       </c>
       <c r="M15" t="n">
-        <v>1725000</v>
+        <v>13080</v>
       </c>
       <c r="N15" t="n">
-        <v>49.76</v>
+        <v>3.12</v>
       </c>
       <c r="O15" t="n">
-        <v>2391615128000</v>
+        <v>24617669915</v>
       </c>
       <c r="P15" t="n">
-        <v>2987000</v>
+        <v>20300</v>
       </c>
       <c r="Q15" t="n">
-        <v>403000</v>
+        <v>3020</v>
       </c>
       <c r="R15" t="n">
-        <v>-199000</v>
+        <v>-292000</v>
       </c>
       <c r="S15" t="n">
-        <v>-57000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>외국인 매도세 지속 및 추세선 하향 돌파, 공매도 비판 및 주가 하락에 대한 부정적 전망.</t>
+          <t>최근 주가 하락 및 박스권 흐름에 대한 답답함 표출. 공매도 및 외국인 매도에 대한 의심.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['외국인 수급', '추세선', '공매도']</t>
+          <t>['전선주', '박스권', '공매도']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>006340</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>아톤</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13130</v>
+        <v>6830</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.94%</t>
+          <t>'-2.15%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.06</v>
+        <v>-0.77</v>
       </c>
       <c r="E16" t="n">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="F16" t="n">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="G16" t="n">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="H16" t="n">
-        <v>3.18</v>
+        <v>1.1</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>13390</v>
+        <v>6980</v>
       </c>
       <c r="K16" t="n">
-        <v>13770</v>
+        <v>7000</v>
       </c>
       <c r="L16" t="n">
-        <v>13830</v>
+        <v>7240</v>
       </c>
       <c r="M16" t="n">
-        <v>13080</v>
+        <v>6580</v>
       </c>
       <c r="N16" t="n">
-        <v>3.12</v>
+        <v>1.87</v>
       </c>
       <c r="O16" t="n">
-        <v>24481715595</v>
+        <v>46537493205</v>
       </c>
       <c r="P16" t="n">
-        <v>20300</v>
+        <v>11370</v>
       </c>
       <c r="Q16" t="n">
-        <v>3020</v>
+        <v>3300</v>
       </c>
       <c r="R16" t="n">
-        <v>-292000</v>
+        <v>180000</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>최근 주가 하락 및 박스권 흐름에 대한 답답함 표출. 공매도 및 외국인 매도에 대한 의심.</t>
+          <t>망분리 완화 관련 금융권 공략 소식 및 3분기 역대급 실적 기대감 언급. 라온시큐어와의 비교 및 보안주로서의 성장 가능성 제시. 시가총액 1조 달성.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,11 +1923,11 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['전선주', '박스권', '공매도']</t>
+          <t>['망분리', '보안주', '실적']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>158430</t>
         </is>
       </c>
     </row>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18010</v>
+        <v>17990</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-2.81%</t>
+          <t>'-2.91%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>1.11</v>
       </c>
       <c r="E17" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F17" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G17" t="n">
-        <v>913</v>
+        <v>944</v>
       </c>
       <c r="H17" t="n">
         <v>4.92</v>
@@ -1990,7 +1990,7 @@
         <v>3.81</v>
       </c>
       <c r="O17" t="n">
-        <v>261475524265</v>
+        <v>263399740705</v>
       </c>
       <c r="P17" t="n">
         <v>31500</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>미국 광통신 주가 상승 및 젠슨 황의 지지 언급으로 강세 전망. 외인 매도에도 불구하고 2만원 안착 기대.</t>
+          <t>미국 광통신 주가 호조 및 젠슨 황의 광통신 지지, 2만원 안착 기대감.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['광통신', '미국 증시', '외인']</t>
+          <t>['광통신', '모멘텀', '지지']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>45850</v>
+        <v>45900</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-3.27%</t>
+          <t>'-3.16%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.02</v>
       </c>
       <c r="E18" t="n">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="F18" t="n">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="G18" t="n">
-        <v>2015</v>
+        <v>2024</v>
       </c>
       <c r="H18" t="n">
         <v>14.12</v>
@@ -2082,7 +2082,7 @@
         <v>14.1</v>
       </c>
       <c r="O18" t="n">
-        <v>33997702350</v>
+        <v>34315440550</v>
       </c>
       <c r="P18" t="n">
         <v>69200</v>
@@ -2142,13 +2142,13 @@
         <v>0.01</v>
       </c>
       <c r="E19" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G19" t="n">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="H19" t="n">
         <v>10.78</v>
@@ -2174,7 +2174,7 @@
         <v>10.77</v>
       </c>
       <c r="O19" t="n">
-        <v>85895694500</v>
+        <v>86463480775</v>
       </c>
       <c r="P19" t="n">
         <v>75900</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>가온전선과의 비교 열세 속 하한가 근접, 외인 및 프로그램 매도세 지속. "쪽박전선" 비난.</t>
+          <t>가온전선과의 비교 열위, 기관/외인 매도세 심화 및 급락 우려.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['주가', '기관', '외인']</t>
+          <t>['급락', '매도', '비교']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,11 +2223,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>12340</v>
+        <v>12300</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-5.15%</t>
+          <t>'-5.46%</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2266,7 +2266,7 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>35516702465</v>
+        <v>35718453985</v>
       </c>
       <c r="P20" t="n">
         <v>22250</v>

--- a/data/trending_integrated_20261007_12.xlsx
+++ b/data/trending_integrated_20261007_12.xlsx
@@ -584,7 +584,7 @@
         <v>39</v>
       </c>
       <c r="G2" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H2" t="n">
         <v>3.27</v>
@@ -610,7 +610,7 @@
         <v>3.35</v>
       </c>
       <c r="O2" t="n">
-        <v>26301647954</v>
+        <v>26317821884</v>
       </c>
       <c r="P2" t="n">
         <v>5470</v>
@@ -659,21 +659,21 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8120</v>
+        <v>8240</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+20.30%</t>
+          <t>'+22.07%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="F3" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="G3" t="n">
         <v>186</v>
@@ -693,7 +693,7 @@
         <v>6710</v>
       </c>
       <c r="L3" t="n">
-        <v>8310</v>
+        <v>8380</v>
       </c>
       <c r="M3" t="n">
         <v>6690</v>
@@ -702,7 +702,7 @@
         <v>5.14</v>
       </c>
       <c r="O3" t="n">
-        <v>68937064430</v>
+        <v>83417253705</v>
       </c>
       <c r="P3" t="n">
         <v>23500</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>정부의 용적률 상향 및 그린벨트 해제 관련 뉴스 언급. 성수 메가프로젝트 및 건설 기초 소재 대장주로서의 위치 강조. 10만원 목표가 제시.</t>
+          <t>정부의 용적률 완화 및 그린벨트 해제 기대감 속 성수동 프로젝트 관련 언급, 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['용적률', '그린벨트', '건설']</t>
+          <t>['용적률', '성수동', '건설']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -735,7 +735,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -765,10 +765,10 @@
         <v>73</v>
       </c>
       <c r="F4" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G4" t="n">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="H4" t="n">
         <v>2.82</v>
@@ -794,7 +794,7 @@
         <v>2.42</v>
       </c>
       <c r="O4" t="n">
-        <v>91725587600</v>
+        <v>92065486250</v>
       </c>
       <c r="P4" t="n">
         <v>30100</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16900</v>
+        <v>16870</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+13.65%</t>
+          <t>'+13.45%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.98</v>
       </c>
       <c r="E5" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="F5" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G5" t="n">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="H5" t="n">
         <v>2.37</v>
@@ -886,7 +886,7 @@
         <v>1.39</v>
       </c>
       <c r="O5" t="n">
-        <v>234790001100</v>
+        <v>237880480355</v>
       </c>
       <c r="P5" t="n">
         <v>17590</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>개인정보 유출 이슈에 따른 보안주 강세, 양자보안 기술 공급 논의 및 대장주 부각.</t>
+          <t>개인정보 유출 사고 증가에 따른 보안주 부각, 양자보안 공급 논의 및 AI 보안 시대적 사명 강조.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['보안', '해킹', '양자보안']</t>
+          <t>['보안', '양자보안', 'AI']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2640</v>
+        <v>2610</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+10.69%</t>
+          <t>'+9.43%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -978,7 +978,7 @@
         <v>1.11</v>
       </c>
       <c r="O6" t="n">
-        <v>9047553326</v>
+        <v>9159847871</v>
       </c>
       <c r="P6" t="n">
         <v>4760</v>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10530</v>
+        <v>10480</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+8.89%</t>
+          <t>'+8.38%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1070,7 +1070,7 @@
         <v>4.84</v>
       </c>
       <c r="O7" t="n">
-        <v>16900250260</v>
+        <v>17179676390</v>
       </c>
       <c r="P7" t="n">
         <v>15900</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>다양한 질병 테마 언급, 페스트/에볼라 확산 관련 기대와 우려 공존.</t>
+          <t>다양한 질병 테마 관련 언급, 페스트 확산 우려 속 기대감 존재.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['테마', '확산', '기대']</t>
+          <t>['테마주', '질병', '기대감']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13220</v>
+        <v>13160</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+7.22%</t>
+          <t>'+6.73%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.31</v>
       </c>
       <c r="E8" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F8" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G8" t="n">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="H8" t="n">
         <v>0.79</v>
@@ -1162,7 +1162,7 @@
         <v>0.48</v>
       </c>
       <c r="O8" t="n">
-        <v>170075291320</v>
+        <v>172806534515</v>
       </c>
       <c r="P8" t="n">
         <v>20850</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>가스터빈 블레이드 납품 개시 및 원전 관련 기대감, 단기 급등 가능성 언급.</t>
+          <t>원전 관련 '가스터빈 블레이드' 납품 개시 뉴스, 주가 상승 기대와 개미 매수세 관찰.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['납품', '원전', '기대']</t>
+          <t>['원전', '터빈 블레이드', '납품']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5080</v>
+        <v>5060</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+1.40%</t>
+          <t>'+1.00%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>3.32</v>
       </c>
       <c r="E9" t="n">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="F9" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G9" t="n">
-        <v>267</v>
+        <v>284</v>
       </c>
       <c r="H9" t="n">
         <v>4.72</v>
@@ -1254,7 +1254,7 @@
         <v>1.4</v>
       </c>
       <c r="O9" t="n">
-        <v>200309958730</v>
+        <v>202189729755</v>
       </c>
       <c r="P9" t="n">
         <v>8100</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 시장 호조 및 2200억 규모 수주 계약 기대감, 주가 상승 전망.</t>
+          <t>미국 증시 호조 속 급등 기대, 2200억 규모 수주 계약 및 공시 가능성 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['수주', '상승', '기대']</t>
+          <t>['수주', '공시', '급등']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>272000</v>
+        <v>272250</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'+0.09%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="G10" t="n">
-        <v>1432</v>
+        <v>1398</v>
       </c>
       <c r="H10" t="n">
         <v>46.37</v>
@@ -1346,7 +1346,7 @@
         <v>46.41</v>
       </c>
       <c r="O10" t="n">
-        <v>2445050826250</v>
+        <v>2486369166750</v>
       </c>
       <c r="P10" t="n">
         <v>374500</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>정치적 이슈와 연계된 부정적 전망, 일부 매수세 유입 기대.</t>
+          <t>정치적 발언과 함께 외인/기관 매도, 주가 상승 기대감 혼재.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['매도', '매수', '정치']</t>
+          <t>['외인', '기관', '매도']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>81000</v>
+        <v>81200</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-0.61%</t>
+          <t>'-0.37%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.03</v>
       </c>
       <c r="E11" t="n">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="F11" t="n">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G11" t="n">
-        <v>721</v>
+        <v>729</v>
       </c>
       <c r="H11" t="n">
         <v>22.59</v>
@@ -1438,7 +1438,7 @@
         <v>22.56</v>
       </c>
       <c r="O11" t="n">
-        <v>125225851150</v>
+        <v>126344058500</v>
       </c>
       <c r="P11" t="n">
         <v>139200</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>구글의 미국 원전 기업 컨스텔레이션과의 전력 구매 계약 발표에 따른 두산에너빌리티 주가 상승 기대감.</t>
+          <t>구글의 미국 최대 원전기업 전력구매 계약에 따른 기대감, 주가 상승 및 공매도 청산 요구.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['원전', '전력구매', '계약']</t>
+          <t>['원전', '전력구매', '구글']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17540</v>
+        <v>17580</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.18%</t>
+          <t>'-0.96%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.11</v>
       </c>
       <c r="E12" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F12" t="n">
         <v>43</v>
       </c>
       <c r="G12" t="n">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="H12" t="n">
         <v>9.5</v>
@@ -1530,7 +1530,7 @@
         <v>9.390000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>42521687825</v>
+        <v>43071046260</v>
       </c>
       <c r="P12" t="n">
         <v>40350</v>
@@ -1575,83 +1575,83 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼천당제약</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>236500</v>
+        <v>1742000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.87%</t>
+          <t>'-1.75%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="E13" t="n">
-        <v>162</v>
+        <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>108</v>
+        <v>436</v>
       </c>
       <c r="G13" t="n">
-        <v>856</v>
+        <v>1643</v>
       </c>
       <c r="H13" t="n">
-        <v>4.12</v>
+        <v>49.71</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>241000</v>
+        <v>1773000</v>
       </c>
       <c r="K13" t="n">
-        <v>253000</v>
+        <v>1728000</v>
       </c>
       <c r="L13" t="n">
-        <v>257000</v>
+        <v>1779000</v>
       </c>
       <c r="M13" t="n">
-        <v>233500</v>
+        <v>1725000</v>
       </c>
       <c r="N13" t="n">
-        <v>4.08</v>
+        <v>49.76</v>
       </c>
       <c r="O13" t="n">
-        <v>79973223500</v>
+        <v>2504938928500</v>
       </c>
       <c r="P13" t="n">
-        <v>1233000</v>
+        <v>2987000</v>
       </c>
       <c r="Q13" t="n">
-        <v>120000</v>
+        <v>403000</v>
       </c>
       <c r="R13" t="n">
-        <v>-49000</v>
+        <v>-199000</v>
       </c>
       <c r="S13" t="n">
-        <v>2000</v>
+        <v>-57000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>경구용 인슐린 10조원대 L/O 예상 및 아일리아 성과 기반 미래 성장 기대. 외인 공매도 숏커버링으로 인한 상승 가능성 언급.</t>
+          <t>정치적 이슈와 함께 외인 매도, 주가 하락 추세 언급 및 공매도 관련 불만 제기.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['L/O', '아일리아', '경구용 인슐린']</t>
+          <t>['외인', '매도', '하락']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,90 +1660,90 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>000250</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼천당제약</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1739000</v>
+        <v>236250</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-1.92%</t>
+          <t>'-1.97%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.05</v>
+        <v>0.04</v>
       </c>
       <c r="E14" t="n">
-        <v>800</v>
+        <v>163</v>
       </c>
       <c r="F14" t="n">
-        <v>436</v>
+        <v>107</v>
       </c>
       <c r="G14" t="n">
-        <v>1639</v>
+        <v>874</v>
       </c>
       <c r="H14" t="n">
-        <v>49.71</v>
+        <v>4.12</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1773000</v>
+        <v>241000</v>
       </c>
       <c r="K14" t="n">
-        <v>1728000</v>
+        <v>253000</v>
       </c>
       <c r="L14" t="n">
-        <v>1779000</v>
+        <v>257000</v>
       </c>
       <c r="M14" t="n">
-        <v>1725000</v>
+        <v>233500</v>
       </c>
       <c r="N14" t="n">
-        <v>49.76</v>
+        <v>4.08</v>
       </c>
       <c r="O14" t="n">
-        <v>2444478998500</v>
+        <v>80842496500</v>
       </c>
       <c r="P14" t="n">
-        <v>2987000</v>
+        <v>1233000</v>
       </c>
       <c r="Q14" t="n">
-        <v>403000</v>
+        <v>120000</v>
       </c>
       <c r="R14" t="n">
-        <v>-199000</v>
+        <v>-49000</v>
       </c>
       <c r="S14" t="n">
-        <v>-57000</v>
+        <v>2000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>외인 매도세 지속 및 추세선 하향 돌파, 정치적 이슈와 함께 부정적 전망.</t>
+          <t>경구용 인슐린 10조원대 L/O 예상 및 아일리아 성과 기반 미래 성장 기대. 외인 공매도 숏커버링으로 인한 상승 가능성 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['매도', '추세', '하락']</t>
+          <t>['L/O', '아일리아', '경구용 인슐린']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>000250</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1774,7 @@
         <v>0.06</v>
       </c>
       <c r="E15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F15" t="n">
         <v>24</v>
@@ -1806,7 +1806,7 @@
         <v>3.12</v>
       </c>
       <c r="O15" t="n">
-        <v>24617669915</v>
+        <v>24762482910</v>
       </c>
       <c r="P15" t="n">
         <v>20300</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6830</v>
+        <v>6760</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-2.15%</t>
+          <t>'-3.15%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.77</v>
       </c>
       <c r="E16" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F16" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G16" t="n">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="H16" t="n">
         <v>1.1</v>
@@ -1898,7 +1898,7 @@
         <v>1.87</v>
       </c>
       <c r="O16" t="n">
-        <v>46537493205</v>
+        <v>53983428120</v>
       </c>
       <c r="P16" t="n">
         <v>11370</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17990</v>
+        <v>17940</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-2.91%</t>
+          <t>'-3.18%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>1.11</v>
       </c>
       <c r="E17" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F17" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G17" t="n">
-        <v>944</v>
+        <v>962</v>
       </c>
       <c r="H17" t="n">
         <v>4.92</v>
@@ -1990,7 +1990,7 @@
         <v>3.81</v>
       </c>
       <c r="O17" t="n">
-        <v>263399740705</v>
+        <v>265232921910</v>
       </c>
       <c r="P17" t="n">
         <v>31500</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>미국 광통신 주가 호조 및 젠슨 황의 광통신 지지, 2만원 안착 기대감.</t>
+          <t>미국 광통신 주가 상승과 함께 국내 주가 상승 기대감, 외인 매도세 관찰.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['광통신', '모멘텀', '지지']</t>
+          <t>['광통신', '미국', '외인']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>45900</v>
+        <v>45800</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-3.16%</t>
+          <t>'-3.38%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.02</v>
       </c>
       <c r="E18" t="n">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="F18" t="n">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="G18" t="n">
-        <v>2024</v>
+        <v>2058</v>
       </c>
       <c r="H18" t="n">
         <v>14.12</v>
@@ -2082,7 +2082,7 @@
         <v>14.1</v>
       </c>
       <c r="O18" t="n">
-        <v>34315440550</v>
+        <v>34571224550</v>
       </c>
       <c r="P18" t="n">
         <v>69200</v>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>30200</v>
+        <v>30150</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-4.88%</t>
+          <t>'-5.04%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.01</v>
       </c>
       <c r="E19" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="F19" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G19" t="n">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="H19" t="n">
         <v>10.78</v>
@@ -2174,7 +2174,7 @@
         <v>10.77</v>
       </c>
       <c r="O19" t="n">
-        <v>86463480775</v>
+        <v>87423305325</v>
       </c>
       <c r="P19" t="n">
         <v>75900</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>가온전선과의 비교 열위, 기관/외인 매도세 심화 및 급락 우려.</t>
+          <t>가온전선과의 비교 속 하락 추세, 개인 매수세와 외인 매도 관찰.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['급락', '매도', '비교']</t>
+          <t>['가온전선', '하락', '외인']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>12300</v>
+        <v>12260</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-5.46%</t>
+          <t>'-5.76%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>1.88</v>
       </c>
       <c r="E20" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F20" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G20" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H20" t="n">
         <v>1.42</v>
@@ -2260,13 +2260,13 @@
         <v>13560</v>
       </c>
       <c r="M20" t="n">
-        <v>12260</v>
+        <v>12250</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>35718453985</v>
+        <v>35987493150</v>
       </c>
       <c r="P20" t="n">
         <v>22250</v>

--- a/data/trending_integrated_20261007_12.xlsx
+++ b/data/trending_integrated_20261007_12.xlsx
@@ -578,13 +578,13 @@
         <v>-0.08</v>
       </c>
       <c r="E2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F2" t="n">
+        <v>40</v>
+      </c>
+      <c r="G2" t="n">
         <v>39</v>
-      </c>
-      <c r="G2" t="n">
-        <v>38</v>
       </c>
       <c r="H2" t="n">
         <v>3.27</v>
@@ -610,7 +610,7 @@
         <v>3.35</v>
       </c>
       <c r="O2" t="n">
-        <v>26317821884</v>
+        <v>26325800314</v>
       </c>
       <c r="P2" t="n">
         <v>5470</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8240</v>
+        <v>8320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+22.07%</t>
+          <t>'+23.26%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="F3" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G3" t="n">
-        <v>186</v>
+        <v>219</v>
       </c>
       <c r="H3" t="n">
         <v>5.12</v>
@@ -693,7 +693,7 @@
         <v>6710</v>
       </c>
       <c r="L3" t="n">
-        <v>8380</v>
+        <v>8390</v>
       </c>
       <c r="M3" t="n">
         <v>6690</v>
@@ -702,7 +702,7 @@
         <v>5.14</v>
       </c>
       <c r="O3" t="n">
-        <v>83417253705</v>
+        <v>88887281135</v>
       </c>
       <c r="P3" t="n">
         <v>23500</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>정부의 용적률 완화 및 그린벨트 해제 기대감 속 성수동 프로젝트 관련 언급, 주가 상승 기대.</t>
+          <t>정부의 도시 규제 완화 정책 및 건설 경기 회복 기대감으로 상승 전망. 차트상 긍정적 흐름과 대규모 프로젝트 수혜 가능성 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['용적률', '성수동', '건설']</t>
+          <t>['도시 규제 완화', '건설 경기', '긍정적 전망']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26200</v>
+        <v>26400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.16%</t>
+          <t>'+15.03%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -768,7 +768,7 @@
         <v>38</v>
       </c>
       <c r="G4" t="n">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="H4" t="n">
         <v>2.82</v>
@@ -794,7 +794,7 @@
         <v>2.42</v>
       </c>
       <c r="O4" t="n">
-        <v>92065486250</v>
+        <v>92619359675</v>
       </c>
       <c r="P4" t="n">
         <v>30100</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16870</v>
+        <v>16770</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+13.45%</t>
+          <t>'+12.78%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.98</v>
       </c>
       <c r="E5" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F5" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G5" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="H5" t="n">
         <v>2.37</v>
@@ -886,7 +886,7 @@
         <v>1.39</v>
       </c>
       <c r="O5" t="n">
-        <v>237880480355</v>
+        <v>238936186690</v>
       </c>
       <c r="P5" t="n">
         <v>17590</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2610</v>
+        <v>2605</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+9.43%</t>
+          <t>'+9.22%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.29</v>
       </c>
       <c r="E6" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F6" t="n">
         <v>20</v>
       </c>
       <c r="G6" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H6" t="n">
         <v>0.82</v>
@@ -978,7 +978,7 @@
         <v>1.11</v>
       </c>
       <c r="O6" t="n">
-        <v>9159847871</v>
+        <v>9196041777</v>
       </c>
       <c r="P6" t="n">
         <v>4760</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10480</v>
+        <v>10490</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+8.38%</t>
+          <t>'+8.48%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.17</v>
       </c>
       <c r="E7" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F7" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G7" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H7" t="n">
         <v>5.01</v>
@@ -1070,7 +1070,7 @@
         <v>4.84</v>
       </c>
       <c r="O7" t="n">
-        <v>17179676390</v>
+        <v>17363808180</v>
       </c>
       <c r="P7" t="n">
         <v>15900</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13160</v>
+        <v>13260</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+6.73%</t>
+          <t>'+7.54%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.31</v>
       </c>
       <c r="E8" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F8" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G8" t="n">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="H8" t="n">
         <v>0.79</v>
@@ -1162,7 +1162,7 @@
         <v>0.48</v>
       </c>
       <c r="O8" t="n">
-        <v>172806534515</v>
+        <v>173829512250</v>
       </c>
       <c r="P8" t="n">
         <v>20850</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>원전 관련 '가스터빈 블레이드' 납품 개시 뉴스, 주가 상승 기대와 개미 매수세 관찰.</t>
+          <t>한화파워 가스터빈 블레이드 납품 개시 뉴스 기반으로 상승 기대감. 단타 및 개인 매수세 유입과 원전 관련주로서의 기대감 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['원전', '터빈 블레이드', '납품']</t>
+          <t>['가스터빈', '납품 개시', '원전']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5060</v>
+        <v>5100</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+1.00%</t>
+          <t>'+1.80%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>3.32</v>
       </c>
       <c r="E9" t="n">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="F9" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="G9" t="n">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="H9" t="n">
         <v>4.72</v>
@@ -1254,7 +1254,7 @@
         <v>1.4</v>
       </c>
       <c r="O9" t="n">
-        <v>202189729755</v>
+        <v>203428943380</v>
       </c>
       <c r="P9" t="n">
         <v>8100</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 증시 호조 속 급등 기대, 2200억 규모 수주 계약 및 공시 가능성 언급.</t>
+          <t>미국 시장 강세와 2200억 규모의 수주 계약 공시 가능성에 대한 기대감으로 상승 전망. 주포의 움직임과 긍정적인 수급을 근거로 제시.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['수주', '공시', '급등']</t>
+          <t>['수주 계약', '미국 시장', '긍정적 전망']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>272250</v>
+        <v>272750</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.09%</t>
+          <t>'+0.28%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="G10" t="n">
-        <v>1398</v>
+        <v>1400</v>
       </c>
       <c r="H10" t="n">
         <v>46.37</v>
@@ -1346,7 +1346,7 @@
         <v>46.41</v>
       </c>
       <c r="O10" t="n">
-        <v>2486369166750</v>
+        <v>2516987985000</v>
       </c>
       <c r="P10" t="n">
         <v>374500</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>정치적 발언과 함께 외인/기관 매도, 주가 상승 기대감 혼재.</t>
+          <t>정치적 이슈와 매도세를 언급하며 삼성전자 주가 상승에 대한 회의적인 전망 제시. 외인·기관의 매도 흐름과 부정적 뉴스를 근거로 제시.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['외인', '기관', '매도']</t>
+          <t>['매도세', '정치적 이슈', '주가 전망']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>81200</v>
+        <v>81400</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-0.37%</t>
+          <t>'-0.12%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.03</v>
       </c>
       <c r="E11" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F11" t="n">
         <v>157</v>
       </c>
       <c r="G11" t="n">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H11" t="n">
         <v>22.59</v>
@@ -1438,7 +1438,7 @@
         <v>22.56</v>
       </c>
       <c r="O11" t="n">
-        <v>126344058500</v>
+        <v>127426591350</v>
       </c>
       <c r="P11" t="n">
         <v>139200</v>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17580</v>
+        <v>17590</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.96%</t>
+          <t>'-0.90%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1504,7 +1504,7 @@
         <v>43</v>
       </c>
       <c r="G12" t="n">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="H12" t="n">
         <v>9.5</v>
@@ -1530,7 +1530,7 @@
         <v>9.390000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>43071046260</v>
+        <v>43351975490</v>
       </c>
       <c r="P12" t="n">
         <v>40350</v>
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1742000</v>
+        <v>1746000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.75%</t>
+          <t>'-1.52%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1593,10 +1593,10 @@
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="G13" t="n">
-        <v>1643</v>
+        <v>1636</v>
       </c>
       <c r="H13" t="n">
         <v>49.71</v>
@@ -1622,7 +1622,7 @@
         <v>49.76</v>
       </c>
       <c r="O13" t="n">
-        <v>2504938928500</v>
+        <v>2539819161500</v>
       </c>
       <c r="P13" t="n">
         <v>2987000</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>정치적 이슈와 함께 외인 매도, 주가 하락 추세 언급 및 공매도 관련 불만 제기.</t>
+          <t>외국인 매도세 지속과 나스닥 하락 영향으로 하락세 전망. 정치적 이슈와 공매도 관련 부정적 언급 다수.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['외인', '매도', '하락']</t>
+          <t>['외국인 매도', '나스닥', '하락 전망']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>236250</v>
+        <v>237250</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-1.97%</t>
+          <t>'-1.56%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.04</v>
       </c>
       <c r="E14" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F14" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G14" t="n">
-        <v>874</v>
+        <v>867</v>
       </c>
       <c r="H14" t="n">
         <v>4.12</v>
@@ -1714,7 +1714,7 @@
         <v>4.08</v>
       </c>
       <c r="O14" t="n">
-        <v>80842496500</v>
+        <v>81293712500</v>
       </c>
       <c r="P14" t="n">
         <v>1233000</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>경구용 인슐린 10조원대 L/O 예상 및 아일리아 성과 기반 미래 성장 기대. 외인 공매도 숏커버링으로 인한 상승 가능성 언급.</t>
+          <t>아일리아 및 경구용 인슐린 파이프라인에 대한 기대감으로 상승 전망. 외국인 공매도 숏커버링 및 대규모 기술이전 가능성 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['L/O', '아일리아', '경구용 인슐린']</t>
+          <t>['아일리아', '경구용 인슐린', '기술이전']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13120</v>
+        <v>13150</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-2.02%</t>
+          <t>'-1.79%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1806,7 +1806,7 @@
         <v>3.12</v>
       </c>
       <c r="O15" t="n">
-        <v>24762482910</v>
+        <v>24944271795</v>
       </c>
       <c r="P15" t="n">
         <v>20300</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6760</v>
+        <v>6800</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-3.15%</t>
+          <t>'-2.58%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.77</v>
       </c>
       <c r="E16" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F16" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G16" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H16" t="n">
         <v>1.1</v>
@@ -1898,7 +1898,7 @@
         <v>1.87</v>
       </c>
       <c r="O16" t="n">
-        <v>53983428120</v>
+        <v>54495132070</v>
       </c>
       <c r="P16" t="n">
         <v>11370</v>
@@ -1958,13 +1958,13 @@
         <v>1.11</v>
       </c>
       <c r="E17" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F17" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G17" t="n">
-        <v>962</v>
+        <v>978</v>
       </c>
       <c r="H17" t="n">
         <v>4.92</v>
@@ -1990,7 +1990,7 @@
         <v>3.81</v>
       </c>
       <c r="O17" t="n">
-        <v>265232921910</v>
+        <v>266697376630</v>
       </c>
       <c r="P17" t="n">
         <v>31500</v>
@@ -2050,13 +2050,13 @@
         <v>0.02</v>
       </c>
       <c r="E18" t="n">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F18" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G18" t="n">
-        <v>2058</v>
+        <v>2075</v>
       </c>
       <c r="H18" t="n">
         <v>14.12</v>
@@ -2082,7 +2082,7 @@
         <v>14.1</v>
       </c>
       <c r="O18" t="n">
-        <v>34571224550</v>
+        <v>34991073300</v>
       </c>
       <c r="P18" t="n">
         <v>69200</v>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>30150</v>
+        <v>30300</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-5.04%</t>
+          <t>'-4.57%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.01</v>
       </c>
       <c r="E19" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F19" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G19" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H19" t="n">
         <v>10.78</v>
@@ -2174,7 +2174,7 @@
         <v>10.77</v>
       </c>
       <c r="O19" t="n">
-        <v>87423305325</v>
+        <v>88180378450</v>
       </c>
       <c r="P19" t="n">
         <v>75900</v>
@@ -2223,11 +2223,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>12260</v>
+        <v>12390</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-5.76%</t>
+          <t>'-4.77%</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2240,7 +2240,7 @@
         <v>55</v>
       </c>
       <c r="G20" t="n">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="H20" t="n">
         <v>1.42</v>
@@ -2260,13 +2260,13 @@
         <v>13560</v>
       </c>
       <c r="M20" t="n">
-        <v>12250</v>
+        <v>12220</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>35987493150</v>
+        <v>36223963980</v>
       </c>
       <c r="P20" t="n">
         <v>22250</v>

--- a/data/trending_integrated_20261007_12.xlsx
+++ b/data/trending_integrated_20261007_12.xlsx
@@ -578,13 +578,13 @@
         <v>-0.08</v>
       </c>
       <c r="E2" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F2" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G2" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H2" t="n">
         <v>3.27</v>
@@ -610,7 +610,7 @@
         <v>3.35</v>
       </c>
       <c r="O2" t="n">
-        <v>26325800314</v>
+        <v>26328281114</v>
       </c>
       <c r="P2" t="n">
         <v>5470</v>
@@ -670,13 +670,13 @@
         <v>-0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F3" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G3" t="n">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="H3" t="n">
         <v>5.12</v>
@@ -693,7 +693,7 @@
         <v>6710</v>
       </c>
       <c r="L3" t="n">
-        <v>8390</v>
+        <v>8450</v>
       </c>
       <c r="M3" t="n">
         <v>6690</v>
@@ -702,7 +702,7 @@
         <v>5.14</v>
       </c>
       <c r="O3" t="n">
-        <v>88887281135</v>
+        <v>95644320345</v>
       </c>
       <c r="P3" t="n">
         <v>23500</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>정부의 도시 규제 완화 정책 및 건설 경기 회복 기대감으로 상승 전망. 차트상 긍정적 흐름과 대규모 프로젝트 수혜 가능성 언급.</t>
+          <t>정부의 용적률 상향 및 그린벨트 해제 가능성 언급과 함께 건설 기초 소재 대장주로서의 상승 기대감이 높아짐.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['도시 규제 완화', '건설 경기', '긍정적 전망']</t>
+          <t>['용적률', '건설', '시멘트']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26400</v>
+        <v>26450</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.03%</t>
+          <t>'+15.25%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.4</v>
       </c>
       <c r="E4" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G4" t="n">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="H4" t="n">
         <v>2.82</v>
@@ -794,7 +794,7 @@
         <v>2.42</v>
       </c>
       <c r="O4" t="n">
-        <v>92619359675</v>
+        <v>93612705475</v>
       </c>
       <c r="P4" t="n">
         <v>30100</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16770</v>
+        <v>16650</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+12.78%</t>
+          <t>'+11.97%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.98</v>
       </c>
       <c r="E5" t="n">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="F5" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G5" t="n">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="H5" t="n">
         <v>2.37</v>
@@ -886,7 +886,7 @@
         <v>1.39</v>
       </c>
       <c r="O5" t="n">
-        <v>238936186690</v>
+        <v>240189358650</v>
       </c>
       <c r="P5" t="n">
         <v>17590</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>개인정보 유출 사고 증가에 따른 보안주 부각, 양자보안 공급 논의 및 AI 보안 시대적 사명 강조.</t>
+          <t>개인정보 유출 및 해킹 이슈로 인한 보안 강화 필요성이 부각되며, AI 보안 관련 긍정적 전망이 제기됨.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['보안', '양자보안', 'AI']</t>
+          <t>['보안', '해킹', 'AI']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -946,13 +946,13 @@
         <v>-0.29</v>
       </c>
       <c r="E6" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F6" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G6" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="H6" t="n">
         <v>0.82</v>
@@ -978,7 +978,7 @@
         <v>1.11</v>
       </c>
       <c r="O6" t="n">
-        <v>9196041777</v>
+        <v>9231976430</v>
       </c>
       <c r="P6" t="n">
         <v>4760</v>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10490</v>
+        <v>10510</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+8.48%</t>
+          <t>'+8.69%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1044,7 +1044,7 @@
         <v>68</v>
       </c>
       <c r="G7" t="n">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="H7" t="n">
         <v>5.01</v>
@@ -1070,7 +1070,7 @@
         <v>4.84</v>
       </c>
       <c r="O7" t="n">
-        <v>17363808180</v>
+        <v>17469046420</v>
       </c>
       <c r="P7" t="n">
         <v>15900</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13260</v>
+        <v>13230</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+7.54%</t>
+          <t>'+7.30%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.31</v>
       </c>
       <c r="E8" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F8" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G8" t="n">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="H8" t="n">
         <v>0.79</v>
@@ -1162,7 +1162,7 @@
         <v>0.48</v>
       </c>
       <c r="O8" t="n">
-        <v>173829512250</v>
+        <v>175525153200</v>
       </c>
       <c r="P8" t="n">
         <v>20850</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>한화파워 가스터빈 블레이드 납품 개시 뉴스 기반으로 상승 기대감. 단타 및 개인 매수세 유입과 원전 관련주로서의 기대감 언급.</t>
+          <t>한화파워 가스터빈 블레이드 납품 개시 소식이 있으며, 원전 관련주로서의 잠재력에 대한 기대가 존재함.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['가스터빈', '납품 개시', '원전']</t>
+          <t>['원전', '가스터빈', '납품']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5100</v>
+        <v>5180</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+1.80%</t>
+          <t>'+3.39%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>3.32</v>
       </c>
       <c r="E9" t="n">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="F9" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G9" t="n">
-        <v>302</v>
+        <v>342</v>
       </c>
       <c r="H9" t="n">
         <v>4.72</v>
@@ -1254,7 +1254,7 @@
         <v>1.4</v>
       </c>
       <c r="O9" t="n">
-        <v>203428943380</v>
+        <v>206865603900</v>
       </c>
       <c r="P9" t="n">
         <v>8100</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 시장 강세와 2200억 규모의 수주 계약 공시 가능성에 대한 기대감으로 상승 전망. 주포의 움직임과 긍정적인 수급을 근거로 제시.</t>
+          <t>해외 증시 호조 속 2200억 규모의 수주 계약 가능성에 대한 기대감이 높으며, 주가 상승 전망이 우세함.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['수주 계약', '미국 시장', '긍정적 전망']</t>
+          <t>['수주', '공시', '주포']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>272750</v>
+        <v>272250</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.28%</t>
+          <t>'+0.09%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="G10" t="n">
-        <v>1400</v>
+        <v>1369</v>
       </c>
       <c r="H10" t="n">
         <v>46.37</v>
@@ -1346,7 +1346,7 @@
         <v>46.41</v>
       </c>
       <c r="O10" t="n">
-        <v>2516987985000</v>
+        <v>2568268843250</v>
       </c>
       <c r="P10" t="n">
         <v>374500</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>정치적 이슈와 매도세를 언급하며 삼성전자 주가 상승에 대한 회의적인 전망 제시. 외인·기관의 매도 흐름과 부정적 뉴스를 근거로 제시.</t>
+          <t>정치적 이슈와 연관된 부정적 언급이 다수이며, 외국인 및 기관 매도에 대한 부정적 전망이 혼재함.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['매도세', '정치적 이슈', '주가 전망']</t>
+          <t>['외국인', '기관', '정치']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>81400</v>
+        <v>81100</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-0.12%</t>
+          <t>'-0.49%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.03</v>
       </c>
       <c r="E11" t="n">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F11" t="n">
         <v>157</v>
       </c>
       <c r="G11" t="n">
-        <v>730</v>
+        <v>739</v>
       </c>
       <c r="H11" t="n">
         <v>22.59</v>
@@ -1438,7 +1438,7 @@
         <v>22.56</v>
       </c>
       <c r="O11" t="n">
-        <v>127426591350</v>
+        <v>128373556150</v>
       </c>
       <c r="P11" t="n">
         <v>139200</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17590</v>
+        <v>17570</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.90%</t>
+          <t>'-1.01%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.11</v>
       </c>
       <c r="E12" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F12" t="n">
         <v>43</v>
       </c>
       <c r="G12" t="n">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="H12" t="n">
         <v>9.5</v>
@@ -1530,7 +1530,7 @@
         <v>9.390000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>43351975490</v>
+        <v>43734894100</v>
       </c>
       <c r="P12" t="n">
         <v>40350</v>
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1746000</v>
+        <v>1741000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.52%</t>
+          <t>'-1.80%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1593,10 +1593,10 @@
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="G13" t="n">
-        <v>1636</v>
+        <v>1652</v>
       </c>
       <c r="H13" t="n">
         <v>49.71</v>
@@ -1622,7 +1622,7 @@
         <v>49.76</v>
       </c>
       <c r="O13" t="n">
-        <v>2539819161500</v>
+        <v>2578390626500</v>
       </c>
       <c r="P13" t="n">
         <v>2987000</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>외국인 매도세 지속과 나스닥 하락 영향으로 하락세 전망. 정치적 이슈와 공매도 관련 부정적 언급 다수.</t>
+          <t>외국인 매도세 지속과 공매도에 대한 부정적 언급이 많으며, 엔비디아 관련 기대감과 자사주 매입 효과에 대한 의견이 엇갈림.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['외국인 매도', '나스닥', '하락 전망']</t>
+          <t>['외인', '공매도', '자사주']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>237250</v>
+        <v>236250</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-1.56%</t>
+          <t>'-1.97%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.04</v>
       </c>
       <c r="E14" t="n">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F14" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G14" t="n">
-        <v>867</v>
+        <v>882</v>
       </c>
       <c r="H14" t="n">
         <v>4.12</v>
@@ -1714,7 +1714,7 @@
         <v>4.08</v>
       </c>
       <c r="O14" t="n">
-        <v>81293712500</v>
+        <v>81706934500</v>
       </c>
       <c r="P14" t="n">
         <v>1233000</v>
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13150</v>
+        <v>13140</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-1.79%</t>
+          <t>'-2.16%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1791,28 +1791,28 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>13390</v>
+        <v>13430</v>
       </c>
       <c r="K15" t="n">
-        <v>13770</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>13830</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>13080</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>3.12</v>
       </c>
       <c r="O15" t="n">
-        <v>24944271795</v>
+        <v>25022000000</v>
       </c>
       <c r="P15" t="n">
-        <v>20300</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3020</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>-292000</v>
@@ -1851,31 +1851,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6800</v>
+        <v>17980</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-2.58%</t>
+          <t>'-2.97%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.77</v>
+        <v>1.11</v>
       </c>
       <c r="E16" t="n">
-        <v>77</v>
+        <v>171</v>
       </c>
       <c r="F16" t="n">
-        <v>53</v>
+        <v>118</v>
       </c>
       <c r="G16" t="n">
-        <v>204</v>
+        <v>985</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1</v>
+        <v>4.92</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,91 +1883,91 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>6980</v>
+        <v>18530</v>
       </c>
       <c r="K16" t="n">
-        <v>7000</v>
+        <v>18950</v>
       </c>
       <c r="L16" t="n">
-        <v>7240</v>
+        <v>19870</v>
       </c>
       <c r="M16" t="n">
-        <v>6580</v>
+        <v>17880</v>
       </c>
       <c r="N16" t="n">
-        <v>1.87</v>
+        <v>3.81</v>
       </c>
       <c r="O16" t="n">
-        <v>54495132070</v>
+        <v>268046248275</v>
       </c>
       <c r="P16" t="n">
-        <v>11370</v>
+        <v>31500</v>
       </c>
       <c r="Q16" t="n">
-        <v>3300</v>
+        <v>1272</v>
       </c>
       <c r="R16" t="n">
-        <v>180000</v>
+        <v>-491000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>망분리 완화 관련 금융권 공략 소식 및 3분기 역대급 실적 기대감 언급. 라온시큐어와의 비교 및 보안주로서의 성장 가능성 제시. 시가총액 1조 달성.</t>
+          <t>미국 광통신 주가 상승 및 젠슨 황의 지지에 힘입어 주가 상승 모멘텀이 기대되며, 5만원 목표가 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['망분리', '보안주', '실적']</t>
+          <t>['광통신', '젠슨황', '외인']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>158430</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>아톤</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17940</v>
+        <v>6750</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-3.18%</t>
+          <t>'-3.30%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1.11</v>
+        <v>-0.77</v>
       </c>
       <c r="E17" t="n">
-        <v>169</v>
+        <v>78</v>
       </c>
       <c r="F17" t="n">
-        <v>117</v>
+        <v>54</v>
       </c>
       <c r="G17" t="n">
-        <v>978</v>
+        <v>204</v>
       </c>
       <c r="H17" t="n">
-        <v>4.92</v>
+        <v>1.1</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,60 +1975,60 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>18530</v>
+        <v>6980</v>
       </c>
       <c r="K17" t="n">
-        <v>18950</v>
+        <v>7000</v>
       </c>
       <c r="L17" t="n">
-        <v>19870</v>
+        <v>7240</v>
       </c>
       <c r="M17" t="n">
-        <v>17880</v>
+        <v>6580</v>
       </c>
       <c r="N17" t="n">
-        <v>3.81</v>
+        <v>1.87</v>
       </c>
       <c r="O17" t="n">
-        <v>266697376630</v>
+        <v>54890440490</v>
       </c>
       <c r="P17" t="n">
-        <v>31500</v>
+        <v>11370</v>
       </c>
       <c r="Q17" t="n">
-        <v>1272</v>
+        <v>3300</v>
       </c>
       <c r="R17" t="n">
-        <v>-491000</v>
+        <v>180000</v>
       </c>
       <c r="S17" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>미국 광통신 주가 상승과 함께 국내 주가 상승 기대감, 외인 매도세 관찰.</t>
+          <t>망분리 완화 관련 금융권 공략 소식 및 3분기 역대급 실적 기대감 언급. 라온시큐어와의 비교 및 보안주로서의 성장 가능성 제시. 시가총액 1조 달성.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['광통신', '미국', '외인']</t>
+          <t>['망분리', '보안주', '실적']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>158430</t>
         </is>
       </c>
     </row>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>45800</v>
+        <v>45750</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-3.38%</t>
+          <t>'-3.48%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.02</v>
       </c>
       <c r="E18" t="n">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="F18" t="n">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="G18" t="n">
-        <v>2075</v>
+        <v>2104</v>
       </c>
       <c r="H18" t="n">
         <v>14.12</v>
@@ -2082,7 +2082,7 @@
         <v>14.1</v>
       </c>
       <c r="O18" t="n">
-        <v>34991073300</v>
+        <v>35430137000</v>
       </c>
       <c r="P18" t="n">
         <v>69200</v>
@@ -2131,21 +2131,21 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>30300</v>
+        <v>30250</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-4.57%</t>
+          <t>'-4.72%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.01</v>
       </c>
       <c r="E19" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F19" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G19" t="n">
         <v>256</v>
@@ -2174,7 +2174,7 @@
         <v>10.77</v>
       </c>
       <c r="O19" t="n">
-        <v>88180378450</v>
+        <v>89054756325</v>
       </c>
       <c r="P19" t="n">
         <v>75900</v>
@@ -2223,11 +2223,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>12390</v>
+        <v>12350</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-4.77%</t>
+          <t>'-5.07%</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2240,7 +2240,7 @@
         <v>55</v>
       </c>
       <c r="G20" t="n">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="H20" t="n">
         <v>1.42</v>
@@ -2266,7 +2266,7 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>36223963980</v>
+        <v>36466645140</v>
       </c>
       <c r="P20" t="n">
         <v>22250</v>

--- a/data/trending_integrated_20261007_12.xlsx
+++ b/data/trending_integrated_20261007_12.xlsx
@@ -578,10 +578,10 @@
         <v>-0.08</v>
       </c>
       <c r="E2" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F2" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G2" t="n">
         <v>41</v>
@@ -610,7 +610,7 @@
         <v>3.35</v>
       </c>
       <c r="O2" t="n">
-        <v>26328281114</v>
+        <v>26335178624</v>
       </c>
       <c r="P2" t="n">
         <v>5470</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8320</v>
+        <v>8220</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+23.26%</t>
+          <t>'+21.78%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G3" t="n">
-        <v>243</v>
+        <v>285</v>
       </c>
       <c r="H3" t="n">
         <v>5.12</v>
@@ -702,7 +702,7 @@
         <v>5.14</v>
       </c>
       <c r="O3" t="n">
-        <v>95644320345</v>
+        <v>99869228435</v>
       </c>
       <c r="P3" t="n">
         <v>23500</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>정부의 용적률 상향 및 그린벨트 해제 가능성 언급과 함께 건설 기초 소재 대장주로서의 상승 기대감이 높아짐.</t>
+          <t>정부의 용적률 완화 및 개발 사업 기대감으로 인한 급등. 상승 초입 및 목표가 상향 전망.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['용적률', '건설', '시멘트']</t>
+          <t>['용적률 완화', '개발 사업', '상승 초입']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26450</v>
+        <v>26650</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.25%</t>
+          <t>'+16.12%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.4</v>
       </c>
       <c r="E4" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F4" t="n">
         <v>39</v>
       </c>
       <c r="G4" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="H4" t="n">
         <v>2.82</v>
@@ -794,7 +794,7 @@
         <v>2.42</v>
       </c>
       <c r="O4" t="n">
-        <v>93612705475</v>
+        <v>94614507300</v>
       </c>
       <c r="P4" t="n">
         <v>30100</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16650</v>
+        <v>16790</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+11.97%</t>
+          <t>'+12.91%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.98</v>
       </c>
       <c r="E5" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="F5" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G5" t="n">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="H5" t="n">
         <v>2.37</v>
@@ -886,7 +886,7 @@
         <v>1.39</v>
       </c>
       <c r="O5" t="n">
-        <v>240189358650</v>
+        <v>242727611210</v>
       </c>
       <c r="P5" t="n">
         <v>17590</v>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2605</v>
+        <v>2610</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+9.22%</t>
+          <t>'+9.43%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -952,7 +952,7 @@
         <v>22</v>
       </c>
       <c r="G6" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H6" t="n">
         <v>0.82</v>
@@ -978,7 +978,7 @@
         <v>1.11</v>
       </c>
       <c r="O6" t="n">
-        <v>9231976430</v>
+        <v>9263566278</v>
       </c>
       <c r="P6" t="n">
         <v>4760</v>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10510</v>
+        <v>10500</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+8.69%</t>
+          <t>'+8.58%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1044,7 +1044,7 @@
         <v>68</v>
       </c>
       <c r="G7" t="n">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="H7" t="n">
         <v>5.01</v>
@@ -1070,7 +1070,7 @@
         <v>4.84</v>
       </c>
       <c r="O7" t="n">
-        <v>17469046420</v>
+        <v>17578276280</v>
       </c>
       <c r="P7" t="n">
         <v>15900</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>다양한 질병 테마 관련 언급, 페스트 확산 우려 속 기대감 존재.</t>
+          <t>각종 질병 테마로 인한 변동성. 페스트 관련주로 부각되며 단기 급등 후 차익실현 매물 출회 가능성.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['테마주', '질병', '기대감']</t>
+          <t>['만능 테마주', '페스트', '변동성']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13230</v>
+        <v>13200</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+7.30%</t>
+          <t>'+7.06%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.31</v>
       </c>
       <c r="E8" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F8" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G8" t="n">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="H8" t="n">
         <v>0.79</v>
@@ -1162,7 +1162,7 @@
         <v>0.48</v>
       </c>
       <c r="O8" t="n">
-        <v>175525153200</v>
+        <v>176826981170</v>
       </c>
       <c r="P8" t="n">
         <v>20850</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>한화파워 가스터빈 블레이드 납품 개시 소식이 있으며, 원전 관련주로서의 잠재력에 대한 기대가 존재함.</t>
+          <t>삼미금속, 가스터빈 블레이드 납품 개시 뉴스 기반 상승 기대. 변동성 속 매수 의견.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['원전', '가스터빈', '납품']</t>
+          <t>['가스터빈', '납품 개시', '매수']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5180</v>
+        <v>5270</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.39%</t>
+          <t>'+5.19%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>3.32</v>
       </c>
       <c r="E9" t="n">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="F9" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G9" t="n">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="H9" t="n">
         <v>4.72</v>
@@ -1254,7 +1254,7 @@
         <v>1.4</v>
       </c>
       <c r="O9" t="n">
-        <v>206865603900</v>
+        <v>212948078795</v>
       </c>
       <c r="P9" t="n">
         <v>8100</v>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>272250</v>
+        <v>272750</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.09%</t>
+          <t>'+0.28%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="G10" t="n">
-        <v>1369</v>
+        <v>1327</v>
       </c>
       <c r="H10" t="n">
         <v>46.37</v>
@@ -1346,7 +1346,7 @@
         <v>46.41</v>
       </c>
       <c r="O10" t="n">
-        <v>2568268843250</v>
+        <v>2621033698500</v>
       </c>
       <c r="P10" t="n">
         <v>374500</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>정치적 이슈와 연관된 부정적 언급이 다수이며, 외국인 및 기관 매도에 대한 부정적 전망이 혼재함.</t>
+          <t>정치적 이슈와 외국인/기관 매도세로 인한 주가 하락 우려. 다만, 일부 긍정적 전망도 존재.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['외국인', '기관', '정치']</t>
+          <t>['외국인 매도', '기관 매도', '정치 리스크']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1406,13 +1406,13 @@
         <v>0.03</v>
       </c>
       <c r="E11" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="F11" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G11" t="n">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="H11" t="n">
         <v>22.59</v>
@@ -1438,7 +1438,7 @@
         <v>22.56</v>
       </c>
       <c r="O11" t="n">
-        <v>128373556150</v>
+        <v>129192673650</v>
       </c>
       <c r="P11" t="n">
         <v>139200</v>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17570</v>
+        <v>17540</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.01%</t>
+          <t>'-1.18%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1504,7 +1504,7 @@
         <v>43</v>
       </c>
       <c r="G12" t="n">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="H12" t="n">
         <v>9.5</v>
@@ -1530,7 +1530,7 @@
         <v>9.390000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>43734894100</v>
+        <v>44355970955</v>
       </c>
       <c r="P12" t="n">
         <v>40350</v>
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1741000</v>
+        <v>13170</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.80%</t>
+          <t>'-1.64%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.05</v>
+        <v>0.06</v>
       </c>
       <c r="E13" t="n">
-        <v>800</v>
+        <v>52</v>
       </c>
       <c r="F13" t="n">
-        <v>437</v>
+        <v>24</v>
       </c>
       <c r="G13" t="n">
-        <v>1652</v>
+        <v>84</v>
       </c>
       <c r="H13" t="n">
-        <v>49.71</v>
+        <v>3.18</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,143 +1607,143 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1773000</v>
+        <v>13390</v>
       </c>
       <c r="K13" t="n">
-        <v>1728000</v>
+        <v>13770</v>
       </c>
       <c r="L13" t="n">
-        <v>1779000</v>
+        <v>13830</v>
       </c>
       <c r="M13" t="n">
-        <v>1725000</v>
+        <v>13080</v>
       </c>
       <c r="N13" t="n">
-        <v>49.76</v>
+        <v>3.12</v>
       </c>
       <c r="O13" t="n">
-        <v>2578390626500</v>
+        <v>25113416170</v>
       </c>
       <c r="P13" t="n">
-        <v>2987000</v>
+        <v>20300</v>
       </c>
       <c r="Q13" t="n">
-        <v>403000</v>
+        <v>3020</v>
       </c>
       <c r="R13" t="n">
-        <v>-199000</v>
+        <v>-292000</v>
       </c>
       <c r="S13" t="n">
-        <v>-57000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>외국인 매도세 지속과 공매도에 대한 부정적 언급이 많으며, 엔비디아 관련 기대감과 자사주 매입 효과에 대한 의견이 엇갈림.</t>
+          <t>최근 주가 하락 및 박스권 흐름에 대한 답답함 표출. 공매도 및 외국인 매도에 대한 의심.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['외인', '공매도', '자사주']</t>
+          <t>['전선주', '박스권', '공매도']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>006340</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼천당제약</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>236250</v>
+        <v>1743000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-1.97%</t>
+          <t>'-1.69%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="E14" t="n">
-        <v>168</v>
+        <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>109</v>
+        <v>440</v>
       </c>
       <c r="G14" t="n">
-        <v>882</v>
+        <v>1694</v>
       </c>
       <c r="H14" t="n">
-        <v>4.12</v>
+        <v>49.71</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>241000</v>
+        <v>1773000</v>
       </c>
       <c r="K14" t="n">
-        <v>253000</v>
+        <v>1728000</v>
       </c>
       <c r="L14" t="n">
-        <v>257000</v>
+        <v>1779000</v>
       </c>
       <c r="M14" t="n">
-        <v>233500</v>
+        <v>1725000</v>
       </c>
       <c r="N14" t="n">
-        <v>4.08</v>
+        <v>49.76</v>
       </c>
       <c r="O14" t="n">
-        <v>81706934500</v>
+        <v>2635946877000</v>
       </c>
       <c r="P14" t="n">
-        <v>1233000</v>
+        <v>2987000</v>
       </c>
       <c r="Q14" t="n">
-        <v>120000</v>
+        <v>403000</v>
       </c>
       <c r="R14" t="n">
-        <v>-49000</v>
+        <v>-199000</v>
       </c>
       <c r="S14" t="n">
-        <v>2000</v>
+        <v>-57000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>아일리아 및 경구용 인슐린 파이프라인에 대한 기대감으로 상승 전망. 외국인 공매도 숏커버링 및 대규모 기술이전 가능성 언급.</t>
+          <t>외국인 매도세와 정치적 이슈로 인한 하락세 지속. 공매도 및 자사주 매입 효과에 대한 의문 제기.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['아일리아', '경구용 인슐린', '기술이전']</t>
+          <t>['외국인 매도', '공매도', '정치 리스크']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,86 +1752,86 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>000250</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>삼천당제약</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13140</v>
+        <v>235750</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-2.16%</t>
+          <t>'-2.18%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="E15" t="n">
-        <v>50</v>
+        <v>168</v>
       </c>
       <c r="F15" t="n">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="G15" t="n">
-        <v>82</v>
+        <v>880</v>
       </c>
       <c r="H15" t="n">
-        <v>3.18</v>
+        <v>4.12</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>13430</v>
+        <v>241000</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>253000</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>257000</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>233500</v>
       </c>
       <c r="N15" t="n">
-        <v>3.12</v>
+        <v>4.08</v>
       </c>
       <c r="O15" t="n">
-        <v>25022000000</v>
+        <v>82517946500</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1233000</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>120000</v>
       </c>
       <c r="R15" t="n">
-        <v>-292000</v>
+        <v>-49000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>최근 주가 하락 및 박스권 흐름에 대한 답답함 표출. 공매도 및 외국인 매도에 대한 의심.</t>
+          <t>경구용 인슐린 기술 수출 기대감 및 아일리아 계약 기반 상승 전망. 공매도 세력과의 공방 속 거래량 증가.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['전선주', '박스권', '공매도']</t>
+          <t>['기술 수출', '아일리아', '공매도']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>000250</t>
         </is>
       </c>
     </row>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17980</v>
+        <v>18040</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-2.97%</t>
+          <t>'-2.64%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>1.11</v>
       </c>
       <c r="E16" t="n">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="F16" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G16" t="n">
-        <v>985</v>
+        <v>999</v>
       </c>
       <c r="H16" t="n">
         <v>4.92</v>
@@ -1898,7 +1898,7 @@
         <v>3.81</v>
       </c>
       <c r="O16" t="n">
-        <v>268046248275</v>
+        <v>268962398865</v>
       </c>
       <c r="P16" t="n">
         <v>31500</v>
@@ -1943,31 +1943,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6750</v>
+        <v>46050</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-3.30%</t>
+          <t>'-2.85%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.77</v>
+        <v>0.02</v>
       </c>
       <c r="E17" t="n">
-        <v>78</v>
+        <v>318</v>
       </c>
       <c r="F17" t="n">
-        <v>54</v>
+        <v>184</v>
       </c>
       <c r="G17" t="n">
-        <v>204</v>
+        <v>2139</v>
       </c>
       <c r="H17" t="n">
-        <v>1.1</v>
+        <v>14.12</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,47 +1975,47 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>6980</v>
+        <v>47400</v>
       </c>
       <c r="K17" t="n">
-        <v>7000</v>
+        <v>46350</v>
       </c>
       <c r="L17" t="n">
-        <v>7240</v>
+        <v>47850</v>
       </c>
       <c r="M17" t="n">
-        <v>6580</v>
+        <v>45650</v>
       </c>
       <c r="N17" t="n">
-        <v>1.87</v>
+        <v>14.1</v>
       </c>
       <c r="O17" t="n">
-        <v>54890440490</v>
+        <v>35905753075</v>
       </c>
       <c r="P17" t="n">
-        <v>11370</v>
+        <v>69200</v>
       </c>
       <c r="Q17" t="n">
-        <v>3300</v>
+        <v>24150</v>
       </c>
       <c r="R17" t="n">
-        <v>180000</v>
+        <v>3000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>망분리 완화 관련 금융권 공략 소식 및 3분기 역대급 실적 기대감 언급. 라온시큐어와의 비교 및 보안주로서의 성장 가능성 제시. 시가총액 1조 달성.</t>
+          <t>FDA 승인 가능성 90% 이상 전망 및 2~3조원 매출 기대감. 공매도와의 공방 속 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['망분리', '보안주', '실적']</t>
+          <t>['FDA', '간암', '공매도']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2023,43 +2023,43 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>158430</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>아톤</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>45750</v>
+        <v>6760</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-3.48%</t>
+          <t>'-3.15%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.02</v>
+        <v>-0.77</v>
       </c>
       <c r="E18" t="n">
-        <v>310</v>
+        <v>80</v>
       </c>
       <c r="F18" t="n">
-        <v>182</v>
+        <v>55</v>
       </c>
       <c r="G18" t="n">
-        <v>2104</v>
+        <v>206</v>
       </c>
       <c r="H18" t="n">
-        <v>14.12</v>
+        <v>1.1</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,47 +2067,47 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>47400</v>
+        <v>6980</v>
       </c>
       <c r="K18" t="n">
-        <v>46350</v>
+        <v>7000</v>
       </c>
       <c r="L18" t="n">
-        <v>47850</v>
+        <v>7240</v>
       </c>
       <c r="M18" t="n">
-        <v>45650</v>
+        <v>6580</v>
       </c>
       <c r="N18" t="n">
-        <v>14.1</v>
+        <v>1.87</v>
       </c>
       <c r="O18" t="n">
-        <v>35430137000</v>
+        <v>55238104480</v>
       </c>
       <c r="P18" t="n">
-        <v>69200</v>
+        <v>11370</v>
       </c>
       <c r="Q18" t="n">
-        <v>24150</v>
+        <v>3300</v>
       </c>
       <c r="R18" t="n">
-        <v>3000</v>
+        <v>180000</v>
       </c>
       <c r="S18" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>FDA 승인 가능성 90% 이상 전망 및 2~3조원 매출 기대감. 공매도와의 공방 속 주가 상승 기대.</t>
+          <t>실적 개선 기대에도 불구하고 주가 부진. 망분리 완화 정책 수혜 기대와 라온시큐어 비교 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['FDA', '간암', '공매도']</t>
+          <t>['실적 개선', '망분리 완화', '주가 부진']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>158430</t>
         </is>
       </c>
     </row>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>30250</v>
+        <v>30350</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-4.72%</t>
+          <t>'-4.41%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.01</v>
       </c>
       <c r="E19" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F19" t="n">
         <v>67</v>
       </c>
       <c r="G19" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H19" t="n">
         <v>10.78</v>
@@ -2174,7 +2174,7 @@
         <v>10.77</v>
       </c>
       <c r="O19" t="n">
-        <v>89054756325</v>
+        <v>89850240375</v>
       </c>
       <c r="P19" t="n">
         <v>75900</v>
@@ -2223,11 +2223,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>12350</v>
+        <v>12340</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-5.07%</t>
+          <t>'-5.15%</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2240,7 +2240,7 @@
         <v>55</v>
       </c>
       <c r="G20" t="n">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="H20" t="n">
         <v>1.42</v>
@@ -2266,7 +2266,7 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>36466645140</v>
+        <v>36702757125</v>
       </c>
       <c r="P20" t="n">
         <v>22250</v>
